--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA361"/>
+  <dimension ref="A1:AA363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31851,6 +31851,180 @@
         <v>365.26</v>
       </c>
       <c r="AA361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="C362" t="n">
+        <v>362.14</v>
+      </c>
+      <c r="D362" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="E362" t="n">
+        <v>350.09</v>
+      </c>
+      <c r="F362" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="G362" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="H362" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="I362" t="n">
+        <v>358.93</v>
+      </c>
+      <c r="J362" t="n">
+        <v>356.17</v>
+      </c>
+      <c r="K362" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="L362" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="M362" t="n">
+        <v>331.77</v>
+      </c>
+      <c r="N362" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="O362" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="P362" t="n">
+        <v>326.05</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>321.18</v>
+      </c>
+      <c r="R362" t="n">
+        <v>317.85</v>
+      </c>
+      <c r="S362" t="n">
+        <v>318.2</v>
+      </c>
+      <c r="T362" t="n">
+        <v>323.49</v>
+      </c>
+      <c r="U362" t="n">
+        <v>330.98</v>
+      </c>
+      <c r="V362" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="W362" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="X362" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:16+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="C363" t="n">
+        <v>359.03</v>
+      </c>
+      <c r="D363" t="n">
+        <v>354.04</v>
+      </c>
+      <c r="E363" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="F363" t="n">
+        <v>347.29</v>
+      </c>
+      <c r="G363" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="H363" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="I363" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="J363" t="n">
+        <v>352.08</v>
+      </c>
+      <c r="K363" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="L363" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="M363" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="N363" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="O363" t="n">
+        <v>326.94</v>
+      </c>
+      <c r="P363" t="n">
+        <v>325.43</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>318.51</v>
+      </c>
+      <c r="R363" t="n">
+        <v>316.82</v>
+      </c>
+      <c r="S363" t="n">
+        <v>316.92</v>
+      </c>
+      <c r="T363" t="n">
+        <v>321.55</v>
+      </c>
+      <c r="U363" t="n">
+        <v>328.72</v>
+      </c>
+      <c r="V363" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="W363" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="X363" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="AA363" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31867,7 +32041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35560,6 +35734,26 @@
       </c>
       <c r="B369" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -35728,28 +35922,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01101968889954341</v>
+        <v>0.005282488912054935</v>
       </c>
       <c r="J2" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>5.452387843363216e-05</v>
+        <v>1.259220772575897e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>9.025804625930196</v>
+        <v>9.056182556869301</v>
       </c>
       <c r="N2" t="n">
-        <v>131.1002128204803</v>
+        <v>131.5239797890047</v>
       </c>
       <c r="O2" t="n">
-        <v>11.44990012272947</v>
+        <v>11.46839046200489</v>
       </c>
       <c r="P2" t="n">
-        <v>348.8614427560146</v>
+        <v>348.6993979938838</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35806,28 +36000,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04626286065812223</v>
+        <v>0.06346921188268402</v>
       </c>
       <c r="J3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007514511913270239</v>
+        <v>0.001422010022535947</v>
       </c>
       <c r="M3" t="n">
-        <v>10.40710904426312</v>
+        <v>10.4318490377484</v>
       </c>
       <c r="N3" t="n">
-        <v>167.5378223341733</v>
+        <v>167.8961141241181</v>
       </c>
       <c r="O3" t="n">
-        <v>12.94364022731524</v>
+        <v>12.95747329243314</v>
       </c>
       <c r="P3" t="n">
-        <v>344.025624377145</v>
+        <v>343.8545936659155</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35884,28 +36078,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06252415621219169</v>
+        <v>-0.0479611495457497</v>
       </c>
       <c r="J4" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001318364317433041</v>
+        <v>0.000782738830302443</v>
       </c>
       <c r="M4" t="n">
-        <v>10.60051566146894</v>
+        <v>10.61644939783833</v>
       </c>
       <c r="N4" t="n">
-        <v>174.3261153289691</v>
+        <v>174.2839193929317</v>
       </c>
       <c r="O4" t="n">
-        <v>13.20326154133777</v>
+        <v>13.20166350854814</v>
       </c>
       <c r="P4" t="n">
-        <v>344.1596577301717</v>
+        <v>344.014902198112</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35962,28 +36156,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1678492066671967</v>
+        <v>-0.1553538271497742</v>
       </c>
       <c r="J5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008987473276307445</v>
+        <v>0.007785538300381201</v>
       </c>
       <c r="M5" t="n">
-        <v>10.59973620121179</v>
+        <v>10.60293815654047</v>
       </c>
       <c r="N5" t="n">
-        <v>182.8753909454846</v>
+        <v>182.5559203710974</v>
       </c>
       <c r="O5" t="n">
-        <v>13.52314279098925</v>
+        <v>13.51132563337504</v>
       </c>
       <c r="P5" t="n">
-        <v>341.5514325989755</v>
+        <v>341.4272328853874</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36040,28 +36234,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1016953269010374</v>
+        <v>-0.0908617777126725</v>
       </c>
       <c r="J6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004394177450307679</v>
+        <v>0.003545975404572688</v>
       </c>
       <c r="M6" t="n">
-        <v>8.968089751544804</v>
+        <v>8.975702870572396</v>
       </c>
       <c r="N6" t="n">
-        <v>137.93897031931</v>
+        <v>137.6952970489402</v>
       </c>
       <c r="O6" t="n">
-        <v>11.74474224150151</v>
+        <v>11.73436393883112</v>
       </c>
       <c r="P6" t="n">
-        <v>342.0132751407505</v>
+        <v>341.905593190031</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36118,28 +36312,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1459454744729721</v>
+        <v>-0.1334508791870365</v>
       </c>
       <c r="J7" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K7" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009721581938218482</v>
+        <v>0.008208567123235921</v>
       </c>
       <c r="M7" t="n">
-        <v>8.766510161217884</v>
+        <v>8.789773211242158</v>
       </c>
       <c r="N7" t="n">
-        <v>127.7252579511644</v>
+        <v>127.7117861344354</v>
       </c>
       <c r="O7" t="n">
-        <v>11.30155997865624</v>
+        <v>11.30096394713457</v>
       </c>
       <c r="P7" t="n">
-        <v>343.6460496732728</v>
+        <v>343.5218580730499</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36196,28 +36390,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1338965352002463</v>
+        <v>-0.1205118270094401</v>
       </c>
       <c r="J8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007607717713717377</v>
+        <v>0.006221016978269933</v>
       </c>
       <c r="M8" t="n">
-        <v>9.273726175404839</v>
+        <v>9.295220216557356</v>
       </c>
       <c r="N8" t="n">
-        <v>137.6711107159239</v>
+        <v>137.6964881187109</v>
       </c>
       <c r="O8" t="n">
-        <v>11.73333331649297</v>
+        <v>11.73441469007768</v>
       </c>
       <c r="P8" t="n">
-        <v>343.5302620380788</v>
+        <v>343.3972211200935</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36274,28 +36468,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0824987851662181</v>
+        <v>-0.07268140973003565</v>
       </c>
       <c r="J9" t="n">
+        <v>362</v>
+      </c>
+      <c r="K9" t="n">
         <v>360</v>
       </c>
-      <c r="K9" t="n">
-        <v>358</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.003928831450086268</v>
+        <v>0.003080880278205078</v>
       </c>
       <c r="M9" t="n">
-        <v>7.96758650832807</v>
+        <v>7.977573238724363</v>
       </c>
       <c r="N9" t="n">
-        <v>101.8174337253424</v>
+        <v>101.6870206746602</v>
       </c>
       <c r="O9" t="n">
-        <v>10.09046251295462</v>
+        <v>10.08399824844591</v>
       </c>
       <c r="P9" t="n">
-        <v>350.5399384348547</v>
+        <v>350.4422807064623</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36352,28 +36546,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.169511805026398</v>
+        <v>-0.161514447973985</v>
       </c>
       <c r="J10" t="n">
+        <v>362</v>
+      </c>
+      <c r="K10" t="n">
         <v>360</v>
       </c>
-      <c r="K10" t="n">
-        <v>358</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.01738396397720887</v>
+        <v>0.0159730506589939</v>
       </c>
       <c r="M10" t="n">
-        <v>8.017123771179422</v>
+        <v>8.01653775637697</v>
       </c>
       <c r="N10" t="n">
-        <v>95.83739463349303</v>
+        <v>95.60390103274969</v>
       </c>
       <c r="O10" t="n">
-        <v>9.78965753402503</v>
+        <v>9.777724737010635</v>
       </c>
       <c r="P10" t="n">
-        <v>351.5736292179668</v>
+        <v>351.4940785745314</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36430,28 +36624,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07577523570912448</v>
+        <v>-0.07339899035838213</v>
       </c>
       <c r="J11" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00396789597582814</v>
+        <v>0.003773105387395947</v>
       </c>
       <c r="M11" t="n">
-        <v>7.482832891382808</v>
+        <v>7.453537379843191</v>
       </c>
       <c r="N11" t="n">
-        <v>85.06988179072783</v>
+        <v>84.64409829466049</v>
       </c>
       <c r="O11" t="n">
-        <v>9.223333550876703</v>
+        <v>9.200222730709323</v>
       </c>
       <c r="P11" t="n">
-        <v>346.1353234934018</v>
+        <v>346.1117349460612</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36508,28 +36702,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06233200224959422</v>
+        <v>-0.06334515073130696</v>
       </c>
       <c r="J12" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00342337824092187</v>
+        <v>0.003583305271229298</v>
       </c>
       <c r="M12" t="n">
-        <v>6.429413868390246</v>
+        <v>6.398961557683148</v>
       </c>
       <c r="N12" t="n">
-        <v>66.75536010147442</v>
+        <v>66.39587817203946</v>
       </c>
       <c r="O12" t="n">
-        <v>8.17039534548203</v>
+        <v>8.148366595339182</v>
       </c>
       <c r="P12" t="n">
-        <v>340.5678887234131</v>
+        <v>340.5779554586975</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36586,28 +36780,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06795023281796882</v>
+        <v>-0.07139648477783758</v>
       </c>
       <c r="J13" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K13" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004779937934965894</v>
+        <v>0.005341808011074867</v>
       </c>
       <c r="M13" t="n">
-        <v>5.925130415031568</v>
+        <v>5.907374186068033</v>
       </c>
       <c r="N13" t="n">
-        <v>56.8512693429745</v>
+        <v>56.58791401896444</v>
       </c>
       <c r="O13" t="n">
-        <v>7.539978073109662</v>
+        <v>7.522493869652832</v>
       </c>
       <c r="P13" t="n">
-        <v>336.0563165884769</v>
+        <v>336.090582376937</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36664,28 +36858,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1085423811957636</v>
+        <v>-0.1117830494439265</v>
       </c>
       <c r="J14" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K14" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01152410792116465</v>
+        <v>0.01237141324646907</v>
       </c>
       <c r="M14" t="n">
-        <v>6.037767949630569</v>
+        <v>6.020008005597823</v>
       </c>
       <c r="N14" t="n">
-        <v>59.48844330400362</v>
+        <v>59.20540353804902</v>
       </c>
       <c r="O14" t="n">
-        <v>7.712875164554631</v>
+        <v>7.694504762364438</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6282945152455</v>
+        <v>334.6605097569421</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36742,28 +36936,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0251775213590641</v>
+        <v>0.01843579610775062</v>
       </c>
       <c r="J15" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K15" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0003968803277059063</v>
+        <v>0.0002153248098526461</v>
       </c>
       <c r="M15" t="n">
-        <v>7.80112723489118</v>
+        <v>7.794534655394087</v>
       </c>
       <c r="N15" t="n">
-        <v>93.98728967983855</v>
+        <v>93.6636973536128</v>
       </c>
       <c r="O15" t="n">
-        <v>9.694704207960063</v>
+        <v>9.678000689895244</v>
       </c>
       <c r="P15" t="n">
-        <v>332.6055524362569</v>
+        <v>332.6725698151192</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36820,28 +37014,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09468214193257375</v>
+        <v>0.08603147055398046</v>
       </c>
       <c r="J16" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K16" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004580884708567101</v>
+        <v>0.003826483467918362</v>
       </c>
       <c r="M16" t="n">
-        <v>8.342253883466467</v>
+        <v>8.338292570881984</v>
       </c>
       <c r="N16" t="n">
-        <v>114.6747792100298</v>
+        <v>114.3628434548757</v>
       </c>
       <c r="O16" t="n">
-        <v>10.70863106143964</v>
+        <v>10.69405645463291</v>
       </c>
       <c r="P16" t="n">
-        <v>330.8884671717648</v>
+        <v>330.9744601202819</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36898,28 +37092,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1884054798209998</v>
+        <v>0.1760446722213673</v>
       </c>
       <c r="J17" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K17" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01340194132937544</v>
+        <v>0.01183038544550996</v>
       </c>
       <c r="M17" t="n">
-        <v>9.694619720329918</v>
+        <v>9.70229091003978</v>
       </c>
       <c r="N17" t="n">
-        <v>153.8277735446868</v>
+        <v>153.6432463720163</v>
       </c>
       <c r="O17" t="n">
-        <v>12.40273250314973</v>
+        <v>12.39529129839296</v>
       </c>
       <c r="P17" t="n">
-        <v>325.7669494727131</v>
+        <v>325.8898278946656</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36976,28 +37170,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3088278203890699</v>
+        <v>0.2953414509293732</v>
       </c>
       <c r="J18" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K18" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03315820525889657</v>
+        <v>0.03067649285958318</v>
       </c>
       <c r="M18" t="n">
-        <v>10.48660638567918</v>
+        <v>10.49384747860083</v>
       </c>
       <c r="N18" t="n">
-        <v>163.7089347371804</v>
+        <v>163.5863069489197</v>
       </c>
       <c r="O18" t="n">
-        <v>12.79487923886663</v>
+        <v>12.79008627605458</v>
       </c>
       <c r="P18" t="n">
-        <v>321.0178242412326</v>
+        <v>321.1518871041835</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37054,28 +37248,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.363639270971991</v>
+        <v>0.350801997766632</v>
       </c>
       <c r="J19" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K19" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04734095447024478</v>
+        <v>0.04459268243434134</v>
       </c>
       <c r="M19" t="n">
-        <v>10.28848407180487</v>
+        <v>10.29066619138317</v>
       </c>
       <c r="N19" t="n">
-        <v>156.6452362858247</v>
+        <v>156.4891324761715</v>
       </c>
       <c r="O19" t="n">
-        <v>12.51579946650731</v>
+        <v>12.50956164204692</v>
       </c>
       <c r="P19" t="n">
-        <v>319.1925867493561</v>
+        <v>319.3201979648234</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37132,28 +37326,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4801375432885924</v>
+        <v>0.4695335735423857</v>
       </c>
       <c r="J20" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K20" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07769504793135851</v>
+        <v>0.07529564851460613</v>
       </c>
       <c r="M20" t="n">
-        <v>10.2924577305054</v>
+        <v>10.28275025837634</v>
       </c>
       <c r="N20" t="n">
-        <v>161.0970853940224</v>
+        <v>160.6946535878583</v>
       </c>
       <c r="O20" t="n">
-        <v>12.69240266435092</v>
+        <v>12.67653949577164</v>
       </c>
       <c r="P20" t="n">
-        <v>319.0248233005729</v>
+        <v>319.1302361643171</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37210,28 +37404,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4806013525486827</v>
+        <v>0.4714728868870395</v>
       </c>
       <c r="J21" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K21" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08232978037975291</v>
+        <v>0.08031038817504565</v>
       </c>
       <c r="M21" t="n">
-        <v>9.910769419894036</v>
+        <v>9.892921098077968</v>
       </c>
       <c r="N21" t="n">
-        <v>151.5565841053936</v>
+        <v>151.0838707783692</v>
       </c>
       <c r="O21" t="n">
-        <v>12.31083198266444</v>
+        <v>12.29161790727198</v>
       </c>
       <c r="P21" t="n">
-        <v>325.0297568448402</v>
+        <v>325.1205034011485</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37288,28 +37482,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5857954768124171</v>
+        <v>0.5786532945326412</v>
       </c>
       <c r="J22" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K22" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1231338960682501</v>
+        <v>0.1218052517031067</v>
       </c>
       <c r="M22" t="n">
-        <v>9.829302879026072</v>
+        <v>9.797309089267486</v>
       </c>
       <c r="N22" t="n">
-        <v>144.0209375616183</v>
+        <v>143.4453572493026</v>
       </c>
       <c r="O22" t="n">
-        <v>12.00087236669144</v>
+        <v>11.97686758920306</v>
       </c>
       <c r="P22" t="n">
-        <v>333.2140998404797</v>
+        <v>333.2851296236017</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37366,28 +37560,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4329004631119723</v>
+        <v>0.4342195877570273</v>
       </c>
       <c r="J23" t="n">
+        <v>362</v>
+      </c>
+      <c r="K23" t="n">
         <v>360</v>
       </c>
-      <c r="K23" t="n">
-        <v>358</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.07563706051976871</v>
+        <v>0.07702292096908903</v>
       </c>
       <c r="M23" t="n">
-        <v>9.322569035038612</v>
+        <v>9.280059374231129</v>
       </c>
       <c r="N23" t="n">
-        <v>135.1400424919167</v>
+        <v>134.4074953570876</v>
       </c>
       <c r="O23" t="n">
-        <v>11.62497494586189</v>
+        <v>11.59342466043091</v>
       </c>
       <c r="P23" t="n">
-        <v>341.9867910908812</v>
+        <v>341.9736749212118</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37444,28 +37638,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5237453319427837</v>
+        <v>0.5185202139915005</v>
       </c>
       <c r="J24" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K24" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07553765101979648</v>
+        <v>0.07505621955832442</v>
       </c>
       <c r="M24" t="n">
-        <v>11.75525212505103</v>
+        <v>11.70953206244265</v>
       </c>
       <c r="N24" t="n">
-        <v>197.6247040779506</v>
+        <v>196.65053630064</v>
       </c>
       <c r="O24" t="n">
-        <v>14.05790539440178</v>
+        <v>14.02321419292453</v>
       </c>
       <c r="P24" t="n">
-        <v>348.3036515477463</v>
+        <v>348.3555930318246</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37522,28 +37716,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6176913728756979</v>
+        <v>0.6156785583050345</v>
       </c>
       <c r="J25" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K25" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1114526492985494</v>
+        <v>0.1121549029416375</v>
       </c>
       <c r="M25" t="n">
-        <v>11.08820888636518</v>
+        <v>11.03373584091131</v>
       </c>
       <c r="N25" t="n">
-        <v>179.5318184901201</v>
+        <v>178.5600009613491</v>
       </c>
       <c r="O25" t="n">
-        <v>13.39894840986113</v>
+        <v>13.36263450676359</v>
       </c>
       <c r="P25" t="n">
-        <v>345.6977525044265</v>
+        <v>345.7177466275401</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37600,28 +37794,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.573041986208882</v>
+        <v>0.5792145201601216</v>
       </c>
       <c r="J26" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K26" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L26" t="n">
-        <v>0.09638677233399129</v>
+        <v>0.09940451143955975</v>
       </c>
       <c r="M26" t="n">
-        <v>11.06971160267853</v>
+        <v>11.0475417260852</v>
       </c>
       <c r="N26" t="n">
-        <v>182.053667491492</v>
+        <v>181.2120150905477</v>
       </c>
       <c r="O26" t="n">
-        <v>13.49272646619252</v>
+        <v>13.4615012197952</v>
       </c>
       <c r="P26" t="n">
-        <v>343.1587536808693</v>
+        <v>343.0973922179905</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37659,7 +37853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA361"/>
+  <dimension ref="A1:AA363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87055,6 +87249,280 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-37.7086845582978,178.5346001223173</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-37.70922252235075,178.53401127358254</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-37.70974307355688,178.53339346976432</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-37.710255865069364,178.53276276650166</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-37.71080770001594,178.53219700876878</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-37.71136945563716,178.53164775832445</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-37.711922909551134,178.53108470689375</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-37.71250071282587,178.53056239796186</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-37.71305516659135,178.52999942449213</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-37.71364197841574,178.52947569135867</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-37.71422365912999,178.52894274963876</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-37.71481312256311,178.52842893504754</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-37.71542155958958,178.52796173272222</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-37.71603910454516,178.5275020830433</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-37.71667241678091,178.52707068475974</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-37.71729629814279,178.52662500887135</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-37.717923082417805,178.526197095737</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>-37.71856316818804,178.52580729695404</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>-37.71921723222261,178.5254712849581</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>-37.719871033131945,178.52513542350846</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>-37.72054560393553,178.52483956974376</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>-37.72122280625637,178.52454750918008</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>-37.72185656329991,178.52414132405607</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>-37.722540800894436,178.52390524390574</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>-37.7232290979648,178.523685579776</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:16+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-37.708671868014065,178.53457901523456</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-37.70920565611242,178.53398322086431</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-37.7097279426629,178.5333683033812</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-37.71023482269283,178.532727767937</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-37.71079001999305,178.53216760259534</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-37.71134770801978,178.53161158672071</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-37.71190381927896,178.53105295508453</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-37.71248097242195,178.53052787565017</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-37.713036374900554,178.52995965948986</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-37.71362595100892,178.52943632758073</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-37.71421517397192,178.5289219098513</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-37.71480816260615,178.52841675325226</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-37.71541889513457,178.52795518873458</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-37.71603638370686,178.52749506852422</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-37.716670122114344,178.52706429297146</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-37.71728664334377,178.526597355294</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-37.7179193578856,178.52618642779322</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>-37.718558539619686,178.52579403959547</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>-37.71920999445658,178.52545131709343</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>-37.71986226487176,178.52511235984275</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>-37.720539888586636,178.52482470090214</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>-37.721212001874804,178.5245194007062</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>-37.721854603849366,178.5241347573878</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>-37.72253624630218,178.52388382226653</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>-37.72322374433009,178.5236597427216</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA363"/>
+  <dimension ref="A1:AA366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32025,6 +32025,267 @@
         <v>362.9</v>
       </c>
       <c r="AA363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:12+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>361.27</v>
+      </c>
+      <c r="C364" t="n">
+        <v>357.53</v>
+      </c>
+      <c r="D364" t="n">
+        <v>353.06</v>
+      </c>
+      <c r="E364" t="n">
+        <v>345.38</v>
+      </c>
+      <c r="F364" t="n">
+        <v>346.59</v>
+      </c>
+      <c r="G364" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="H364" t="n">
+        <v>349.26</v>
+      </c>
+      <c r="I364" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="J364" t="n">
+        <v>351.14</v>
+      </c>
+      <c r="K364" t="n">
+        <v>342.84</v>
+      </c>
+      <c r="L364" t="n">
+        <v>336.04</v>
+      </c>
+      <c r="M364" t="n">
+        <v>329.47</v>
+      </c>
+      <c r="N364" t="n">
+        <v>327.69</v>
+      </c>
+      <c r="O364" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="P364" t="n">
+        <v>324.54</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>317.84</v>
+      </c>
+      <c r="R364" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="S364" t="n">
+        <v>316.02</v>
+      </c>
+      <c r="T364" t="n">
+        <v>320.06</v>
+      </c>
+      <c r="U364" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="V364" t="n">
+        <v>341.02</v>
+      </c>
+      <c r="W364" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="X364" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>362.02</v>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="C365" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="D365" t="n">
+        <v>352.27</v>
+      </c>
+      <c r="E365" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="F365" t="n">
+        <v>345.96</v>
+      </c>
+      <c r="G365" t="n">
+        <v>347.03</v>
+      </c>
+      <c r="H365" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="I365" t="n">
+        <v>353.92</v>
+      </c>
+      <c r="J365" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="K365" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="L365" t="n">
+        <v>336.15</v>
+      </c>
+      <c r="M365" t="n">
+        <v>329.25</v>
+      </c>
+      <c r="N365" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="O365" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="P365" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>317.51</v>
+      </c>
+      <c r="R365" t="n">
+        <v>314.92</v>
+      </c>
+      <c r="S365" t="n">
+        <v>314.7</v>
+      </c>
+      <c r="T365" t="n">
+        <v>319.11</v>
+      </c>
+      <c r="U365" t="n">
+        <v>327.49</v>
+      </c>
+      <c r="V365" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="W365" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="X365" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:53:29+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>358.59</v>
+      </c>
+      <c r="C366" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="D366" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="E366" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="F366" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="G366" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="H366" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="I366" t="n">
+        <v>352.14</v>
+      </c>
+      <c r="J366" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="K366" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="L366" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="M366" t="n">
+        <v>328.08</v>
+      </c>
+      <c r="N366" t="n">
+        <v>326.84</v>
+      </c>
+      <c r="O366" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="P366" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>316.95</v>
+      </c>
+      <c r="R366" t="n">
+        <v>313.89</v>
+      </c>
+      <c r="S366" t="n">
+        <v>314.7</v>
+      </c>
+      <c r="T366" t="n">
+        <v>319.11</v>
+      </c>
+      <c r="U366" t="n">
+        <v>327.49</v>
+      </c>
+      <c r="V366" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="W366" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="X366" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="AA366" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32041,7 +32302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35754,6 +36015,36 @@
       </c>
       <c r="B371" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -35922,28 +36213,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005282488912054935</v>
+        <v>0.023990634453107</v>
       </c>
       <c r="J2" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L2" t="n">
-        <v>1.259220772575897e-05</v>
+        <v>0.0002628512689240026</v>
       </c>
       <c r="M2" t="n">
-        <v>9.056182556869301</v>
+        <v>9.073350311844989</v>
       </c>
       <c r="N2" t="n">
-        <v>131.5239797890047</v>
+        <v>131.4853646004953</v>
       </c>
       <c r="O2" t="n">
-        <v>11.46839046200489</v>
+        <v>11.46670678968008</v>
       </c>
       <c r="P2" t="n">
-        <v>348.6993979938838</v>
+        <v>348.5129820984444</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36000,28 +36291,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06346921188268402</v>
+        <v>0.08123150710488426</v>
       </c>
       <c r="J3" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K3" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001422010022535947</v>
+        <v>0.002361199113877333</v>
       </c>
       <c r="M3" t="n">
-        <v>10.4318490377484</v>
+        <v>10.43136207926595</v>
       </c>
       <c r="N3" t="n">
-        <v>167.8961141241181</v>
+        <v>167.458785750754</v>
       </c>
       <c r="O3" t="n">
-        <v>12.95747329243314</v>
+        <v>12.94058676222813</v>
       </c>
       <c r="P3" t="n">
-        <v>343.8545936659155</v>
+        <v>343.6776054551124</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36078,28 +36369,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0479611495457497</v>
+        <v>-0.0332873824924269</v>
       </c>
       <c r="J4" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K4" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000782738830302443</v>
+        <v>0.0003834425227743354</v>
       </c>
       <c r="M4" t="n">
-        <v>10.61644939783833</v>
+        <v>10.60351432692698</v>
       </c>
       <c r="N4" t="n">
-        <v>174.2839193929317</v>
+        <v>173.5044653615162</v>
       </c>
       <c r="O4" t="n">
-        <v>13.20166350854814</v>
+        <v>13.17210937403407</v>
       </c>
       <c r="P4" t="n">
-        <v>344.014902198112</v>
+        <v>343.8686974448657</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36156,28 +36447,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1553538271497742</v>
+        <v>-0.1445992177619305</v>
       </c>
       <c r="J5" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K5" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007785538300381201</v>
+        <v>0.006875132946190576</v>
       </c>
       <c r="M5" t="n">
-        <v>10.60293815654047</v>
+        <v>10.56985231180683</v>
       </c>
       <c r="N5" t="n">
-        <v>182.5559203710974</v>
+        <v>181.4148520033561</v>
       </c>
       <c r="O5" t="n">
-        <v>13.51132563337504</v>
+        <v>13.46903307603616</v>
       </c>
       <c r="P5" t="n">
-        <v>341.4272328853874</v>
+        <v>341.3200849756282</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36234,28 +36525,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0908617777126725</v>
+        <v>-0.08129437219134603</v>
       </c>
       <c r="J6" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003545975404572688</v>
+        <v>0.002892241116811967</v>
       </c>
       <c r="M6" t="n">
-        <v>8.975702870572396</v>
+        <v>8.952562342817817</v>
       </c>
       <c r="N6" t="n">
-        <v>137.6952970489402</v>
+        <v>136.8506166754642</v>
       </c>
       <c r="O6" t="n">
-        <v>11.73436393883112</v>
+        <v>11.69831683087205</v>
       </c>
       <c r="P6" t="n">
-        <v>341.905593190031</v>
+        <v>341.8102751867065</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36312,28 +36603,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1334508791870365</v>
+        <v>-0.1223360904528274</v>
       </c>
       <c r="J7" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K7" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008208567123235921</v>
+        <v>0.007026343739907404</v>
       </c>
       <c r="M7" t="n">
-        <v>8.789773211242158</v>
+        <v>8.781813581327794</v>
       </c>
       <c r="N7" t="n">
-        <v>127.7117861344354</v>
+        <v>127.0386076557221</v>
       </c>
       <c r="O7" t="n">
-        <v>11.30096394713457</v>
+        <v>11.27114047715324</v>
       </c>
       <c r="P7" t="n">
-        <v>343.5218580730499</v>
+        <v>343.411115737306</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36390,28 +36681,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1205118270094401</v>
+        <v>-0.1089986555464857</v>
       </c>
       <c r="J8" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K8" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006221016978269933</v>
+        <v>0.005182584365970633</v>
       </c>
       <c r="M8" t="n">
-        <v>9.295220216557356</v>
+        <v>9.282148734032631</v>
       </c>
       <c r="N8" t="n">
-        <v>137.6964881187109</v>
+        <v>136.9800994541805</v>
       </c>
       <c r="O8" t="n">
-        <v>11.73441469007768</v>
+        <v>11.7038497706601</v>
       </c>
       <c r="P8" t="n">
-        <v>343.3972211200935</v>
+        <v>343.2825174575808</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36468,28 +36759,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07268140973003565</v>
+        <v>-0.06447282253783869</v>
       </c>
       <c r="J9" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K9" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003080880278205078</v>
+        <v>0.002470049047590628</v>
       </c>
       <c r="M9" t="n">
-        <v>7.977573238724363</v>
+        <v>7.957607805230091</v>
       </c>
       <c r="N9" t="n">
-        <v>101.6870206746602</v>
+        <v>101.0535793017687</v>
       </c>
       <c r="O9" t="n">
-        <v>10.08399824844591</v>
+        <v>10.05254093758233</v>
       </c>
       <c r="P9" t="n">
-        <v>350.4422807064623</v>
+        <v>350.3604280154875</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36546,28 +36837,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.161514447973985</v>
+        <v>-0.1566201823554807</v>
       </c>
       <c r="J10" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K10" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0159730506589939</v>
+        <v>0.01532198973963661</v>
       </c>
       <c r="M10" t="n">
-        <v>8.01653775637697</v>
+        <v>7.976997154442151</v>
       </c>
       <c r="N10" t="n">
-        <v>95.60390103274969</v>
+        <v>94.89700135543568</v>
       </c>
       <c r="O10" t="n">
-        <v>9.777724737010635</v>
+        <v>9.741509192904131</v>
       </c>
       <c r="P10" t="n">
-        <v>351.4940785745314</v>
+        <v>351.445286787758</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36624,28 +36915,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07339899035838213</v>
+        <v>-0.0771947103849364</v>
       </c>
       <c r="J11" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K11" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003773105387395947</v>
+        <v>0.004253776719600033</v>
       </c>
       <c r="M11" t="n">
-        <v>7.453537379843191</v>
+        <v>7.409889150360979</v>
       </c>
       <c r="N11" t="n">
-        <v>84.64409829466049</v>
+        <v>83.99878498736277</v>
       </c>
       <c r="O11" t="n">
-        <v>9.200222730709323</v>
+        <v>9.165085105298409</v>
       </c>
       <c r="P11" t="n">
-        <v>346.1117349460612</v>
+        <v>346.1495460244509</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36702,28 +36993,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06334515073130696</v>
+        <v>-0.06902916342072027</v>
       </c>
       <c r="J12" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K12" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003583305271229298</v>
+        <v>0.00433190672436079</v>
       </c>
       <c r="M12" t="n">
-        <v>6.398961557683148</v>
+        <v>6.371358111941173</v>
       </c>
       <c r="N12" t="n">
-        <v>66.39587817203946</v>
+        <v>65.95149667511632</v>
       </c>
       <c r="O12" t="n">
-        <v>8.148366595339182</v>
+        <v>8.121052682695533</v>
       </c>
       <c r="P12" t="n">
-        <v>340.5779554586975</v>
+        <v>340.6345630588502</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36780,28 +37071,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07139648477783758</v>
+        <v>-0.08001332206642438</v>
       </c>
       <c r="J13" t="n">
+        <v>365</v>
+      </c>
+      <c r="K13" t="n">
         <v>362</v>
       </c>
-      <c r="K13" t="n">
-        <v>359</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.005341808011074867</v>
+        <v>0.00680827303408793</v>
       </c>
       <c r="M13" t="n">
-        <v>5.907374186068033</v>
+        <v>5.896947226004958</v>
       </c>
       <c r="N13" t="n">
-        <v>56.58791401896444</v>
+        <v>56.34216437999487</v>
       </c>
       <c r="O13" t="n">
-        <v>7.522493869652832</v>
+        <v>7.506141777237815</v>
       </c>
       <c r="P13" t="n">
-        <v>336.090582376937</v>
+        <v>336.17648146735</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36858,28 +37149,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1117830494439265</v>
+        <v>-0.1187412883274668</v>
       </c>
       <c r="J14" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K14" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01237141324646907</v>
+        <v>0.01418331418980956</v>
       </c>
       <c r="M14" t="n">
-        <v>6.020008005597823</v>
+        <v>6.004121954814238</v>
       </c>
       <c r="N14" t="n">
-        <v>59.20540353804902</v>
+        <v>58.86269611697905</v>
       </c>
       <c r="O14" t="n">
-        <v>7.694504762364438</v>
+        <v>7.672202820375583</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6605097569421</v>
+        <v>334.7298596551242</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36936,28 +37227,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01843579610775062</v>
+        <v>0.006863028540216406</v>
       </c>
       <c r="J15" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K15" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002153248098526461</v>
+        <v>3.03255519383816e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>7.794534655394087</v>
+        <v>7.79235348910909</v>
       </c>
       <c r="N15" t="n">
-        <v>93.6636973536128</v>
+        <v>93.28845948260316</v>
       </c>
       <c r="O15" t="n">
-        <v>9.678000689895244</v>
+        <v>9.658595109155533</v>
       </c>
       <c r="P15" t="n">
-        <v>332.6725698151192</v>
+        <v>332.7878991111978</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37014,28 +37305,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08603147055398046</v>
+        <v>0.07134128853968896</v>
       </c>
       <c r="J16" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K16" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003826483467918362</v>
+        <v>0.002673065930607899</v>
       </c>
       <c r="M16" t="n">
-        <v>8.338292570881984</v>
+        <v>8.341302017765281</v>
       </c>
       <c r="N16" t="n">
-        <v>114.3628434548757</v>
+        <v>114.058582886065</v>
       </c>
       <c r="O16" t="n">
-        <v>10.69405645463291</v>
+        <v>10.67982129466898</v>
       </c>
       <c r="P16" t="n">
-        <v>330.9744601202819</v>
+        <v>331.1208579499916</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37092,28 +37383,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1760446722213673</v>
+        <v>0.1542915788166131</v>
       </c>
       <c r="J17" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K17" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01183038544550996</v>
+        <v>0.009212911015190284</v>
       </c>
       <c r="M17" t="n">
-        <v>9.70229091003978</v>
+        <v>9.729241180753657</v>
       </c>
       <c r="N17" t="n">
-        <v>153.6432463720163</v>
+        <v>153.7751304924464</v>
       </c>
       <c r="O17" t="n">
-        <v>12.39529129839296</v>
+        <v>12.40061008549363</v>
       </c>
       <c r="P17" t="n">
-        <v>325.8898278946656</v>
+        <v>326.1066167513984</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37170,28 +37461,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2953414509293732</v>
+        <v>0.2720025365915872</v>
       </c>
       <c r="J18" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K18" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03067649285958318</v>
+        <v>0.02640524283329537</v>
       </c>
       <c r="M18" t="n">
-        <v>10.49384747860083</v>
+        <v>10.51917819476488</v>
       </c>
       <c r="N18" t="n">
-        <v>163.5863069489197</v>
+        <v>163.852157749895</v>
       </c>
       <c r="O18" t="n">
-        <v>12.79008627605458</v>
+        <v>12.80047490329539</v>
       </c>
       <c r="P18" t="n">
-        <v>321.1518871041835</v>
+        <v>321.384488827157</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37248,28 +37539,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.350801997766632</v>
+        <v>0.3283188852490656</v>
       </c>
       <c r="J19" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K19" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04459268243434134</v>
+        <v>0.03967997156675462</v>
       </c>
       <c r="M19" t="n">
-        <v>10.29066619138317</v>
+        <v>10.30908137313041</v>
       </c>
       <c r="N19" t="n">
-        <v>156.4891324761715</v>
+        <v>156.6947909440006</v>
       </c>
       <c r="O19" t="n">
-        <v>12.50956164204692</v>
+        <v>12.51777899405484</v>
       </c>
       <c r="P19" t="n">
-        <v>319.3201979648234</v>
+        <v>319.5442638887728</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37326,28 +37617,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4695335735423857</v>
+        <v>0.4491515839103944</v>
       </c>
       <c r="J20" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K20" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07529564851460613</v>
+        <v>0.07015696939138449</v>
       </c>
       <c r="M20" t="n">
-        <v>10.28275025837634</v>
+        <v>10.28844725590728</v>
       </c>
       <c r="N20" t="n">
-        <v>160.6946535878583</v>
+        <v>160.5990185842464</v>
       </c>
       <c r="O20" t="n">
-        <v>12.67653949577164</v>
+        <v>12.6727668085642</v>
       </c>
       <c r="P20" t="n">
-        <v>319.1302361643171</v>
+        <v>319.3333608059092</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37404,28 +37695,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4714728868870395</v>
+        <v>0.4545390403203288</v>
       </c>
       <c r="J21" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K21" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08031038817504565</v>
+        <v>0.07608797942477152</v>
       </c>
       <c r="M21" t="n">
-        <v>9.892921098077968</v>
+        <v>9.880190009288411</v>
       </c>
       <c r="N21" t="n">
-        <v>151.0838707783692</v>
+        <v>150.6867768771066</v>
       </c>
       <c r="O21" t="n">
-        <v>12.29161790727198</v>
+        <v>12.27545424320854</v>
       </c>
       <c r="P21" t="n">
-        <v>325.1205034011485</v>
+        <v>325.2892606132303</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37482,28 +37773,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5786532945326412</v>
+        <v>0.5656490993124835</v>
       </c>
       <c r="J22" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K22" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1218052517031067</v>
+        <v>0.1187583791928232</v>
       </c>
       <c r="M22" t="n">
-        <v>9.797309089267486</v>
+        <v>9.75897330727606</v>
       </c>
       <c r="N22" t="n">
-        <v>143.4453572493026</v>
+        <v>142.7622893641621</v>
       </c>
       <c r="O22" t="n">
-        <v>11.97686758920306</v>
+        <v>11.94831742816377</v>
       </c>
       <c r="P22" t="n">
-        <v>333.2851296236017</v>
+        <v>333.4147795780589</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37560,28 +37851,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4342195877570273</v>
+        <v>0.4306405760011405</v>
       </c>
       <c r="J23" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K23" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07702292096908903</v>
+        <v>0.07725797748912144</v>
       </c>
       <c r="M23" t="n">
-        <v>9.280059374231129</v>
+        <v>9.216597788925812</v>
       </c>
       <c r="N23" t="n">
-        <v>134.4074953570876</v>
+        <v>133.3352030159884</v>
       </c>
       <c r="O23" t="n">
-        <v>11.59342466043091</v>
+        <v>11.54708634314251</v>
       </c>
       <c r="P23" t="n">
-        <v>341.9736749212118</v>
+        <v>342.009375092824</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37638,28 +37929,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5185202139915005</v>
+        <v>0.5080652410505776</v>
       </c>
       <c r="J24" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K24" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07505621955832442</v>
+        <v>0.07352932840303761</v>
       </c>
       <c r="M24" t="n">
-        <v>11.70953206244265</v>
+        <v>11.65120660638294</v>
       </c>
       <c r="N24" t="n">
-        <v>196.65053630064</v>
+        <v>195.3566684823569</v>
       </c>
       <c r="O24" t="n">
-        <v>14.02321419292453</v>
+        <v>13.97700498970924</v>
       </c>
       <c r="P24" t="n">
-        <v>348.3555930318246</v>
+        <v>348.4597796020007</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37716,28 +38007,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6156785583050345</v>
+        <v>0.6098223522418047</v>
       </c>
       <c r="J25" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K25" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1121549029416375</v>
+        <v>0.1122033099995179</v>
       </c>
       <c r="M25" t="n">
-        <v>11.03373584091131</v>
+        <v>10.96290433243675</v>
       </c>
       <c r="N25" t="n">
-        <v>178.5600009613491</v>
+        <v>177.1896998087506</v>
       </c>
       <c r="O25" t="n">
-        <v>13.36263450676359</v>
+        <v>13.31126214183879</v>
       </c>
       <c r="P25" t="n">
-        <v>345.7177466275401</v>
+        <v>345.7760524965355</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37794,28 +38085,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5792145201601216</v>
+        <v>0.5830263888120545</v>
       </c>
       <c r="J26" t="n">
+        <v>365</v>
+      </c>
+      <c r="K26" t="n">
         <v>362</v>
       </c>
-      <c r="K26" t="n">
-        <v>359</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.09940451143955975</v>
+        <v>0.1023968613633762</v>
       </c>
       <c r="M26" t="n">
-        <v>11.0475417260852</v>
+        <v>10.98007559234627</v>
       </c>
       <c r="N26" t="n">
-        <v>181.2120150905477</v>
+        <v>179.7574648210421</v>
       </c>
       <c r="O26" t="n">
-        <v>13.4615012197952</v>
+        <v>13.40736606575065</v>
       </c>
       <c r="P26" t="n">
-        <v>343.0973922179905</v>
+        <v>343.0594077323574</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37853,7 +38144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA363"/>
+  <dimension ref="A1:AA366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87523,6 +87814,417 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:12+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-37.708668451398474,178.53457333255963</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-37.709197521267996,178.53396969061882</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-37.70972262786712,178.53335946357876</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-37.71023032135813,178.53272028113315</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-37.710786223668,178.53216128838807</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-37.71134298970708,178.53160373901886</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-37.71189937211186,178.53104555835853</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-37.712476562330124,178.53052016322127</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-37.71303205602571,178.52995052034782</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-37.713620130310254,178.52942203178807</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-37.71421144378038,178.52891274840024</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-37.71480369454455,178.5284057795702</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-37.71541557481318,178.52794703391984</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-37.71603370230055,178.5274881556653</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-37.71666682815684,178.52705511766305</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-37.71728422060281,178.52659041600785</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-37.7179165735259,178.5261784527291</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>-37.71855528515659,178.5257847180161</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>-37.719204435551276,178.5254359809524</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>-37.719858385109006,178.52510215468251</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>-37.72053640457158,178.52481563702028</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>-37.72120597333987,178.5245037169958</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>-37.72184894672379,178.52411579878273</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>-37.72253445699695,178.52387540662318</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>-37.72322174805801,178.52365010856653</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-37.708665577102565,178.534568551897</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-37.7091941588651,178.53396409811816</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-37.70971834349038,178.53335233761646</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-37.71022365070451,178.5327091862327</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-37.710782806975125,178.5321556056021</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-37.71133794599282,178.5315953500973</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-37.7118878745554,178.5310264351197</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-37.71247440978509,178.53051639882176</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-37.71303044793381,178.52994711747604</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-37.713618080768015,178.52941699805874</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-37.71421189468269,178.52891385582836</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-37.7148027927338,178.52840356469875</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-37.71541569778805,178.52794733595</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-37.71603255875948,178.52748520753445</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-37.7166659398985,178.52705264342273</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-37.71728302731233,178.52658699815063</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>-37.717912487386535,178.52616674906454</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>-37.71855051194258,178.52577104636777</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>-37.719200891281666,178.52542620287701</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>-37.719857492763445,178.52509980749582</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>-37.72053636542533,178.52481553517893</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>-37.72120374199843,178.5244979119867</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>-37.721850590134906,178.52412130631018</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>-37.72253441052147,178.52387518803502</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>-37.72321843605927,178.52363412462833</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:53:29+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-37.70865391722062,178.53454915864663</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-37.70918173966469,178.53394344195078</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-37.709703700679995,178.5333279830678</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-37.71021074325747,178.53268771805685</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-37.71076810976881,178.5321311606079</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-37.711327045059676,178.5315772192061</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-37.71187637699533,178.5310073118867</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-37.71246506458799,178.5305000558215</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-37.713019421014955,178.52992378350186</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-37.71360975962406,178.52939656112036</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-37.71420336852781,178.5288929153718</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-37.71479799673956,178.52839178561047</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-37.715412090524616,178.5279384763989</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-37.71603342627341,178.5274874440475</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-37.716665865876955,178.52705243723602</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-37.71728100233429,178.52658119815075</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>-37.717908762851344,178.52615608112356</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>-37.71855051194258,178.52577104636777</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>-37.719200891281666,178.52542620287701</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>-37.719857492763445,178.52509980749582</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>-37.72053636542533,178.52481553517893</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>-37.72120374199843,178.5244979119867</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>-37.721850590134906,178.52412130631018</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>-37.72253441052147,178.52387518803502</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>-37.72321843605927,178.52363412462833</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA366"/>
+  <dimension ref="A1:AA367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32288,6 +32288,93 @@
       <c r="AA366" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>358.43</v>
+      </c>
+      <c r="C367" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="D367" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="E367" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="F367" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="G367" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="H367" t="n">
+        <v>344.74</v>
+      </c>
+      <c r="I367" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="J367" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="K367" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="L367" t="n">
+        <v>332.44</v>
+      </c>
+      <c r="M367" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="N367" t="n">
+        <v>326.51</v>
+      </c>
+      <c r="O367" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="P367" t="n">
+        <v>324.97</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>316.14</v>
+      </c>
+      <c r="R367" t="n">
+        <v>313.42</v>
+      </c>
+      <c r="S367" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="T367" t="n">
+        <v>318.19</v>
+      </c>
+      <c r="U367" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="V367" t="n">
+        <v>338.42</v>
+      </c>
+      <c r="W367" t="n">
+        <v>349.53</v>
+      </c>
+      <c r="X367" t="n">
+        <v>353.64</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>355.48</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>357.14</v>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32302,7 +32389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36045,6 +36132,16 @@
       </c>
       <c r="B374" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -36213,28 +36310,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.023990634453107</v>
+        <v>0.02905452263716864</v>
       </c>
       <c r="J2" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K2" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002628512689240026</v>
+        <v>0.0003873563978415984</v>
       </c>
       <c r="M2" t="n">
-        <v>9.073350311844989</v>
+        <v>9.073144876871082</v>
       </c>
       <c r="N2" t="n">
-        <v>131.4853646004953</v>
+        <v>131.3585273640774</v>
       </c>
       <c r="O2" t="n">
-        <v>11.46670678968008</v>
+        <v>11.46117478115038</v>
       </c>
       <c r="P2" t="n">
-        <v>348.5129820984444</v>
+        <v>348.4623955211644</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36291,28 +36388,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08123150710488426</v>
+        <v>0.08561909976857801</v>
       </c>
       <c r="J3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002361199113877333</v>
+        <v>0.002637127123163219</v>
       </c>
       <c r="M3" t="n">
-        <v>10.43136207926595</v>
+        <v>10.42397857939557</v>
       </c>
       <c r="N3" t="n">
-        <v>167.458785750754</v>
+        <v>167.1757272890516</v>
       </c>
       <c r="O3" t="n">
-        <v>12.94058676222813</v>
+        <v>12.92964528860137</v>
       </c>
       <c r="P3" t="n">
-        <v>343.6776054551124</v>
+        <v>343.6337748476251</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36369,28 +36466,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0332873824924269</v>
+        <v>-0.03011284012546399</v>
       </c>
       <c r="J4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003834425227743354</v>
+        <v>0.0003157362449148771</v>
       </c>
       <c r="M4" t="n">
-        <v>10.60351432692698</v>
+        <v>10.59067826399061</v>
       </c>
       <c r="N4" t="n">
-        <v>173.5044653615162</v>
+        <v>173.1217478292326</v>
       </c>
       <c r="O4" t="n">
-        <v>13.17210937403407</v>
+        <v>13.15757378201744</v>
       </c>
       <c r="P4" t="n">
-        <v>343.8686974448657</v>
+        <v>343.8369848108308</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36447,28 +36544,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1445992177619305</v>
+        <v>-0.142611271183284</v>
       </c>
       <c r="J5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006875132946190576</v>
+        <v>0.006731526167556345</v>
       </c>
       <c r="M5" t="n">
-        <v>10.56985231180683</v>
+        <v>10.55094288033441</v>
       </c>
       <c r="N5" t="n">
-        <v>181.4148520033561</v>
+        <v>180.95500093918</v>
       </c>
       <c r="O5" t="n">
-        <v>13.46903307603616</v>
+        <v>13.45195156619217</v>
       </c>
       <c r="P5" t="n">
-        <v>341.3200849756282</v>
+        <v>341.3002260432083</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36525,28 +36622,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08129437219134603</v>
+        <v>-0.07989555983215198</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002892241116811967</v>
+        <v>0.002812011771770373</v>
       </c>
       <c r="M6" t="n">
-        <v>8.952562342817817</v>
+        <v>8.935462558489068</v>
       </c>
       <c r="N6" t="n">
-        <v>136.8506166754642</v>
+        <v>136.4944420209252</v>
       </c>
       <c r="O6" t="n">
-        <v>11.69831683087205</v>
+        <v>11.68308358358037</v>
       </c>
       <c r="P6" t="n">
-        <v>341.8102751867065</v>
+        <v>341.7963015113534</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36603,28 +36700,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1223360904528274</v>
+        <v>-0.1201879597387629</v>
       </c>
       <c r="J7" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K7" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007026343739907404</v>
+        <v>0.006825998607470796</v>
       </c>
       <c r="M7" t="n">
-        <v>8.781813581327794</v>
+        <v>8.770226366131302</v>
       </c>
       <c r="N7" t="n">
-        <v>127.0386076557221</v>
+        <v>126.7333303744251</v>
       </c>
       <c r="O7" t="n">
-        <v>11.27114047715324</v>
+        <v>11.25758990079249</v>
       </c>
       <c r="P7" t="n">
-        <v>343.411115737306</v>
+        <v>343.3896566180631</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36681,28 +36778,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1089986555464857</v>
+        <v>-0.1065899813620338</v>
       </c>
       <c r="J8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005182584365970633</v>
+        <v>0.004988091716881859</v>
       </c>
       <c r="M8" t="n">
-        <v>9.282148734032631</v>
+        <v>9.270001055416946</v>
       </c>
       <c r="N8" t="n">
-        <v>136.9800994541805</v>
+        <v>136.6584201082767</v>
       </c>
       <c r="O8" t="n">
-        <v>11.7038497706601</v>
+        <v>11.69009923432118</v>
       </c>
       <c r="P8" t="n">
-        <v>343.2825174575808</v>
+        <v>343.25845559477</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36759,28 +36856,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06447282253783869</v>
+        <v>-0.0629006740005176</v>
       </c>
       <c r="J9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K9" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002470049047590628</v>
+        <v>0.002366380197972751</v>
       </c>
       <c r="M9" t="n">
-        <v>7.957607805230091</v>
+        <v>7.944518921755708</v>
       </c>
       <c r="N9" t="n">
-        <v>101.0535793017687</v>
+        <v>100.7984591571694</v>
       </c>
       <c r="O9" t="n">
-        <v>10.05254093758233</v>
+        <v>10.03984358230592</v>
       </c>
       <c r="P9" t="n">
-        <v>350.3604280154875</v>
+        <v>350.3447096286226</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36837,28 +36934,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1566201823554807</v>
+        <v>-0.1567124349031404</v>
       </c>
       <c r="J10" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K10" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01532198973963661</v>
+        <v>0.01544001622962121</v>
       </c>
       <c r="M10" t="n">
-        <v>7.976997154442151</v>
+        <v>7.95550142342473</v>
       </c>
       <c r="N10" t="n">
-        <v>94.89700135543568</v>
+        <v>94.63637277961406</v>
       </c>
       <c r="O10" t="n">
-        <v>9.741509192904131</v>
+        <v>9.728122777782673</v>
       </c>
       <c r="P10" t="n">
-        <v>351.445286787758</v>
+        <v>351.4462091314164</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36915,28 +37012,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0771947103849364</v>
+        <v>-0.0804038487952134</v>
       </c>
       <c r="J11" t="n">
+        <v>366</v>
+      </c>
+      <c r="K11" t="n">
         <v>365</v>
       </c>
-      <c r="K11" t="n">
-        <v>364</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.004253776719600033</v>
+        <v>0.004638503068426281</v>
       </c>
       <c r="M11" t="n">
-        <v>7.409889150360979</v>
+        <v>7.404759792900984</v>
       </c>
       <c r="N11" t="n">
-        <v>83.99878498736277</v>
+        <v>83.8622987485284</v>
       </c>
       <c r="O11" t="n">
-        <v>9.165085105298409</v>
+        <v>9.157636089544528</v>
       </c>
       <c r="P11" t="n">
-        <v>346.1495460244509</v>
+        <v>346.1815744000823</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36993,28 +37090,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06902916342072027</v>
+        <v>-0.07248373118223619</v>
       </c>
       <c r="J12" t="n">
+        <v>366</v>
+      </c>
+      <c r="K12" t="n">
         <v>365</v>
       </c>
-      <c r="K12" t="n">
-        <v>364</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.00433190672436079</v>
+        <v>0.004797923295211559</v>
       </c>
       <c r="M12" t="n">
-        <v>6.371358111941173</v>
+        <v>6.369424122425468</v>
       </c>
       <c r="N12" t="n">
-        <v>65.95149667511632</v>
+        <v>65.87932678357403</v>
       </c>
       <c r="O12" t="n">
-        <v>8.121052682695533</v>
+        <v>8.116608083650092</v>
       </c>
       <c r="P12" t="n">
-        <v>340.6345630588502</v>
+        <v>340.6690409092151</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37071,28 +37168,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08001332206642438</v>
+        <v>-0.08375210367037128</v>
       </c>
       <c r="J13" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K13" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00680827303408793</v>
+        <v>0.00748675063586024</v>
       </c>
       <c r="M13" t="n">
-        <v>5.896947226004958</v>
+        <v>5.897470322095135</v>
       </c>
       <c r="N13" t="n">
-        <v>56.34216437999487</v>
+        <v>56.31455939840231</v>
       </c>
       <c r="O13" t="n">
-        <v>7.506141777237815</v>
+        <v>7.504302725663612</v>
       </c>
       <c r="P13" t="n">
-        <v>336.17648146735</v>
+        <v>336.2138386890426</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37149,28 +37246,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1187412883274668</v>
+        <v>-0.1214757705184785</v>
       </c>
       <c r="J14" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K14" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01418331418980956</v>
+        <v>0.01491454397806724</v>
       </c>
       <c r="M14" t="n">
-        <v>6.004121954814238</v>
+        <v>6.000860620971884</v>
       </c>
       <c r="N14" t="n">
-        <v>58.86269611697905</v>
+        <v>58.76963966851059</v>
       </c>
       <c r="O14" t="n">
-        <v>7.672202820375583</v>
+        <v>7.666135902037649</v>
       </c>
       <c r="P14" t="n">
-        <v>334.7298596551242</v>
+        <v>334.7571762327516</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37227,28 +37324,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.006863028540216406</v>
+        <v>0.003414124534623266</v>
       </c>
       <c r="J15" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K15" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L15" t="n">
-        <v>3.03255519383816e-05</v>
+        <v>7.546099707100851e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>7.79235348910909</v>
+        <v>7.789377320811531</v>
       </c>
       <c r="N15" t="n">
-        <v>93.28845948260316</v>
+        <v>93.14138155042878</v>
       </c>
       <c r="O15" t="n">
-        <v>9.658595109155533</v>
+        <v>9.650978269089034</v>
       </c>
       <c r="P15" t="n">
-        <v>332.7878991111978</v>
+        <v>332.822352527756</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37305,28 +37402,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07134128853968896</v>
+        <v>0.06692805691896661</v>
       </c>
       <c r="J16" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K16" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002673065930607899</v>
+        <v>0.002365290826147004</v>
       </c>
       <c r="M16" t="n">
-        <v>8.341302017765281</v>
+        <v>8.339911869949528</v>
       </c>
       <c r="N16" t="n">
-        <v>114.058582886065</v>
+        <v>113.9234717190389</v>
       </c>
       <c r="O16" t="n">
-        <v>10.67982129466898</v>
+        <v>10.67349388527669</v>
       </c>
       <c r="P16" t="n">
-        <v>331.1208579499916</v>
+        <v>331.1649446822261</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37383,28 +37480,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1542915788166131</v>
+        <v>0.1465632318755261</v>
       </c>
       <c r="J17" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K17" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009212911015190284</v>
+        <v>0.008346255646881406</v>
       </c>
       <c r="M17" t="n">
-        <v>9.729241180753657</v>
+        <v>9.74042218244378</v>
       </c>
       <c r="N17" t="n">
-        <v>153.7751304924464</v>
+        <v>153.8963125963291</v>
       </c>
       <c r="O17" t="n">
-        <v>12.40061008549363</v>
+        <v>12.40549525800277</v>
       </c>
       <c r="P17" t="n">
-        <v>326.1066167513984</v>
+        <v>326.1838203952333</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37461,28 +37558,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2720025365915872</v>
+        <v>0.2636273587119101</v>
       </c>
       <c r="J18" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K18" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02640524283329537</v>
+        <v>0.02491063650751002</v>
       </c>
       <c r="M18" t="n">
-        <v>10.51917819476488</v>
+        <v>10.53026561671082</v>
       </c>
       <c r="N18" t="n">
-        <v>163.852157749895</v>
+        <v>164.0402136887424</v>
       </c>
       <c r="O18" t="n">
-        <v>12.80047490329539</v>
+        <v>12.807818459392</v>
       </c>
       <c r="P18" t="n">
-        <v>321.384488827157</v>
+        <v>321.4681540993045</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37539,28 +37636,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3283188852490656</v>
+        <v>0.3204644714503884</v>
       </c>
       <c r="J19" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K19" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03967997156675462</v>
+        <v>0.03798683019180271</v>
       </c>
       <c r="M19" t="n">
-        <v>10.30908137313041</v>
+        <v>10.31693867077229</v>
       </c>
       <c r="N19" t="n">
-        <v>156.6947909440006</v>
+        <v>156.8258006047972</v>
       </c>
       <c r="O19" t="n">
-        <v>12.51777899405484</v>
+        <v>12.52301084423379</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5442638887728</v>
+        <v>319.6227268990475</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37617,28 +37714,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4491515839103944</v>
+        <v>0.4418891751085148</v>
       </c>
       <c r="J20" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K20" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07015696939138449</v>
+        <v>0.06829163782518533</v>
       </c>
       <c r="M20" t="n">
-        <v>10.28844725590728</v>
+        <v>10.29267696773065</v>
       </c>
       <c r="N20" t="n">
-        <v>160.5990185842464</v>
+        <v>160.6382504790014</v>
       </c>
       <c r="O20" t="n">
-        <v>12.6727668085642</v>
+        <v>12.67431459602457</v>
       </c>
       <c r="P20" t="n">
-        <v>319.3333608059092</v>
+        <v>319.4059098809957</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37695,28 +37792,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4545390403203288</v>
+        <v>0.4480909999579595</v>
       </c>
       <c r="J21" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K21" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07608797942477152</v>
+        <v>0.0743870029654673</v>
       </c>
       <c r="M21" t="n">
-        <v>9.880190009288411</v>
+        <v>9.879090669414175</v>
       </c>
       <c r="N21" t="n">
-        <v>150.6867768771066</v>
+        <v>150.6518953203576</v>
       </c>
       <c r="O21" t="n">
-        <v>12.27545424320854</v>
+        <v>12.27403337621165</v>
       </c>
       <c r="P21" t="n">
-        <v>325.2892606132303</v>
+        <v>325.3536744154786</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37773,28 +37870,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5656490993124835</v>
+        <v>0.5600230542553073</v>
       </c>
       <c r="J22" t="n">
+        <v>366</v>
+      </c>
+      <c r="K22" t="n">
         <v>365</v>
       </c>
-      <c r="K22" t="n">
-        <v>364</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1187583791928232</v>
+        <v>0.1171576403263641</v>
       </c>
       <c r="M22" t="n">
-        <v>9.75897330727606</v>
+        <v>9.750709304914182</v>
       </c>
       <c r="N22" t="n">
-        <v>142.7622893641621</v>
+        <v>142.6586564509897</v>
       </c>
       <c r="O22" t="n">
-        <v>11.94831742816377</v>
+        <v>11.94397992509154</v>
       </c>
       <c r="P22" t="n">
-        <v>333.4147795780589</v>
+        <v>333.4710064025007</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37851,28 +37948,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4306405760011405</v>
+        <v>0.4283813306883344</v>
       </c>
       <c r="J23" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K23" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07725797748912144</v>
+        <v>0.07695533463566473</v>
       </c>
       <c r="M23" t="n">
-        <v>9.216597788925812</v>
+        <v>9.199559313974568</v>
       </c>
       <c r="N23" t="n">
-        <v>133.3352030159884</v>
+        <v>133.015361237217</v>
       </c>
       <c r="O23" t="n">
-        <v>11.54708634314251</v>
+        <v>11.53322856953841</v>
       </c>
       <c r="P23" t="n">
-        <v>342.009375092824</v>
+        <v>342.0319630932619</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37929,28 +38026,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5080652410505776</v>
+        <v>0.503385165452087</v>
       </c>
       <c r="J24" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K24" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07352932840303761</v>
+        <v>0.07265563699001931</v>
       </c>
       <c r="M24" t="n">
-        <v>11.65120660638294</v>
+        <v>11.63619480114214</v>
       </c>
       <c r="N24" t="n">
-        <v>195.3566684823569</v>
+        <v>195.0214236825773</v>
       </c>
       <c r="O24" t="n">
-        <v>13.97700498970924</v>
+        <v>13.9650071135885</v>
       </c>
       <c r="P24" t="n">
-        <v>348.4597796020007</v>
+        <v>348.5065320177993</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38007,28 +38104,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6098223522418047</v>
+        <v>0.6061128826318418</v>
       </c>
       <c r="J25" t="n">
+        <v>366</v>
+      </c>
+      <c r="K25" t="n">
         <v>365</v>
       </c>
-      <c r="K25" t="n">
-        <v>364</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1122033099995179</v>
+        <v>0.1115787878343151</v>
       </c>
       <c r="M25" t="n">
-        <v>10.96290433243675</v>
+        <v>10.94550926829208</v>
       </c>
       <c r="N25" t="n">
-        <v>177.1896998087506</v>
+        <v>176.8293731321155</v>
       </c>
       <c r="O25" t="n">
-        <v>13.31126214183879</v>
+        <v>13.29772059911455</v>
       </c>
       <c r="P25" t="n">
-        <v>345.7760524965355</v>
+        <v>345.8130743606224</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -38085,28 +38182,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5830263888120545</v>
+        <v>0.5821022119837651</v>
       </c>
       <c r="J26" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K26" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1023968613633762</v>
+        <v>0.1027093900224185</v>
       </c>
       <c r="M26" t="n">
-        <v>10.98007559234627</v>
+        <v>10.95325761967512</v>
       </c>
       <c r="N26" t="n">
-        <v>179.7574648210421</v>
+        <v>179.2700621743546</v>
       </c>
       <c r="O26" t="n">
-        <v>13.40736606575065</v>
+        <v>13.3891770536637</v>
       </c>
       <c r="P26" t="n">
-        <v>343.0594077323574</v>
+        <v>343.0686419381267</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -38144,7 +38241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA366"/>
+  <dimension ref="A1:AA367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88225,6 +88322,143 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-37.70865304950835,178.53454771542823</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-37.70917783493706,178.53393694743667</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-37.70969941630105,178.53332085710906</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-37.71020683848267,178.53268122348405</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-37.710762252577936,178.53212141869403</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-37.711321675942145,178.5315682890676</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-37.711874858449384,178.5310047861771</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-37.71246165201536,178.530494087873</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-37.71301321837081,178.52991065814425</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-37.713601069558216,178.5293752181154</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-37.71419668697087,178.52887650530565</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-37.714794266520926,178.52838262409833</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-37.71541073780064,178.52793515406745</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-37.71603527959843,178.52749222205284</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-37.71666841961955,178.52705955067714</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-37.71727807334765,178.5265728088657</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>-37.717907063305795,178.52615121322847</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>-37.718548161495654,178.52576431411725</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>-37.719197458935504,178.52541673358374</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>-37.71985089716417,178.5250824587261</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>-37.72052622654564,178.5247891582688</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>-37.721196695654974,178.52447958038118</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>-37.72184256270102,178.5240944041589</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>-37.72252676530097,178.52383923028992</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>-37.7232106778067,178.5235966828052</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
